--- a/artfynd/A 15648-2023 artfynd.xlsx
+++ b/artfynd/A 15648-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15648-2023 artfynd.xlsx
+++ b/artfynd/A 15648-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98506230</v>
+        <v>98506238</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>765001.5722007178</v>
+        <v>764960</v>
       </c>
       <c r="R2" t="n">
-        <v>7085868.604118194</v>
+        <v>7085981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98506237</v>
+        <v>98506230</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765015.6052562655</v>
+        <v>765002</v>
       </c>
       <c r="R3" t="n">
-        <v>7085949.693342882</v>
+        <v>7085868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>98506235</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>765042.5080570164</v>
+        <v>765042</v>
       </c>
       <c r="R4" t="n">
-        <v>7085805.035326256</v>
+        <v>7085805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98506238</v>
+        <v>98506236</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>764960.0690254085</v>
+        <v>765025</v>
       </c>
       <c r="R5" t="n">
-        <v>7085980.952292365</v>
+        <v>7085819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98506241</v>
+        <v>98506237</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764999.6696533307</v>
+        <v>765015</v>
       </c>
       <c r="R6" t="n">
-        <v>7085859.565056412</v>
+        <v>7085950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1163,7 @@
         <v>98506239</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764990.30827915</v>
+        <v>764990</v>
       </c>
       <c r="R7" t="n">
-        <v>7085975.519338246</v>
+        <v>7085975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,53 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98506236</v>
+        <v>103856804</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vannersmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>765025.3149899223</v>
+        <v>764984</v>
       </c>
       <c r="R8" t="n">
-        <v>7085819.118295616</v>
+        <v>7085956</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1323,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,54 +1355,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103856804</v>
+        <v>98506240</v>
       </c>
       <c r="B9" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vannersmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>764983.5631295651</v>
+        <v>764963</v>
       </c>
       <c r="R9" t="n">
-        <v>7085955.41759234</v>
+        <v>7085902</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,22 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,54 +1452,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103856520</v>
+        <v>98506241</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vannersmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765012.5817030506</v>
+        <v>765000</v>
       </c>
       <c r="R10" t="n">
-        <v>7085890.842694337</v>
+        <v>7085860</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,22 +1517,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,6 +1546,309 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>108738885</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>764965</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7085929</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>108738886</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>764928</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7085958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>108738887</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>764947</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7085976</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15648-2023 artfynd.xlsx
+++ b/artfynd/A 15648-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506235</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506236</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103856804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98506241</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108738885</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108738886</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,8 +1909,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108738887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>